--- a/output/pdf_financials_xlsx/ACQ.xlsx
+++ b/output/pdf_financials_xlsx/ACQ.xlsx
@@ -2712,13 +2712,13 @@
         <v>108.301</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>103.146</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>67.343</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>87.96299999999999</v>
       </c>
     </row>
     <row r="35">
@@ -2842,13 +2842,13 @@
         <v>108.301</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>103.146</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>67.343</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>87.96299999999999</v>
       </c>
     </row>
     <row r="37">
@@ -8666,10 +8666,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-133.485</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-302.213</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -8677,22 +8677,22 @@
         </is>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-266.197</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-257.102</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-797.278</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-698.162</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-689.7140000000001</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-820.913</v>
       </c>
     </row>
     <row r="125">
@@ -8729,10 +8729,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-133.485</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-302.213</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -8740,22 +8740,22 @@
         </is>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-266.197</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-257.102</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-797.278</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-698.162</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-689.7140000000001</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-820.913</v>
       </c>
     </row>
     <row r="126">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -41674,7 +41674,11 @@
           <t>Repayment of indebtedness (Note 23)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -42496,7 +42500,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -46654,7 +46662,11 @@
           <t>Repayment of indebtedness</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -47276,7 +47288,11 @@
           <t>Principal portion of lease payments (Note 23)</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -52518,7 +52534,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -56118,7 +56138,11 @@
           <t>Principal elements of lease payments (20,288)</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ACQ.xlsx
+++ b/output/pdf_financials_xlsx/ACQ.xlsx
@@ -2314,22 +2314,22 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>6.346</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>13.624</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>18.86</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>19.557</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>20.444</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>19.947</v>
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
@@ -2337,19 +2337,19 @@
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>42.131</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>43.692</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.374</v>
+        <v>52.007</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.529</v>
+        <v>59.002</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.503</v>
+        <v>62.265</v>
       </c>
       <c r="S28" s="1" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>30.839</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>50.675</v>
+        <v>57.021</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>86.21599999999999</v>
+        <v>106.66</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-76.871</v>
+        <v>-56.924</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2410,19 +2410,19 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.013</v>
+        <v>40.118</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>220.41</v>
+        <v>264.102</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>120.114</v>
+        <v>171.747</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>81.548</v>
+        <v>140.021</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-60.884</v>
+        <v>0.878</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>2.798706237033783</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3.596420257764151</v>
+        <v>4.046797819792198</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2.779762442125898</v>
+        <v>3.438914610712029</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-2.439744304666049</v>
+        <v>-1.806663173352892</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -2483,19 +2483,19 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-0.06045963741036927</v>
+        <v>1.204927835881368</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4.73652145789705</v>
+        <v>5.675444807737973</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.988438602070417</v>
+        <v>2.843201996351699</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1.266902218383878</v>
+        <v>2.175319020948754</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-1.154954644261108</v>
+        <v>0.01665544605579878</v>
       </c>
       <c r="S30" s="1" t="inlineStr">
         <is>
@@ -7142,22 +7142,22 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>6.346</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>13.624</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>18.86</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>19.557</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>20.444</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>19.947</v>
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
@@ -7165,22 +7165,22 @@
         </is>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>42.131</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>43.692</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>52.007</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>59.002</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>62.265</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>53.451</v>
       </c>
     </row>
     <row r="101">
@@ -7889,31 +7889,31 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>3.304</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.121</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>4.267</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>123.798</v>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
@@ -7921,22 +7921,22 @@
         </is>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>2.399</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.123</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.299</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>63.123</v>
       </c>
       <c r="S112" s="3" t="n">
-        <v>0</v>
+        <v>10.433</v>
       </c>
     </row>
     <row r="113">
@@ -8806,19 +8806,19 @@
         <v>0</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-0.079</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>0</v>
+        <v>-3.247</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>0</v>
+        <v>-3.595</v>
       </c>
       <c r="R126" s="3" t="n">
-        <v>0</v>
+        <v>-4.294</v>
       </c>
       <c r="S126" s="3" t="n">
-        <v>0</v>
+        <v>-3.694</v>
       </c>
     </row>
     <row r="127">
@@ -39374,7 +39374,11 @@
           <t>Depreciation of right-of-use assets (Note 24)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -39476,7 +39480,11 @@
           <t>Depreciation of property and equipment (Note 19)</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -39580,7 +39588,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -40898,7 +40906,11 @@
           <t>Additions to intangible assets (Note 20)</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -41100,7 +41112,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -42402,7 +42418,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -45306,7 +45326,11 @@
           <t>Depreciation of right-of-use assets (Note 23)</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -45408,7 +45432,11 @@
           <t>Depreciation of property and equipment (Note 18)</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -45512,7 +45540,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -46460,7 +46488,11 @@
           <t>Additions to intangible assets (Note 19)</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -47816,7 +47848,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -49498,7 +49530,11 @@
           <t>Dividends paid to non-controlling interests (Note 14)</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -50226,7 +50262,11 @@
           <t>Depreciation of property and equipment (Note 20)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -50330,7 +50370,11 @@
           <t>Depreciation of right-of-use assets (Note 25)</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -53488,7 +53532,11 @@
           <t>Depreciation of property and equipment (Note 21) 19,823</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -53594,7 +53642,11 @@
           <t>Depreciation of right-of-use assets (Note 27) 23,404</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -55078,7 +55130,11 @@
           <t>Proceeds on sale of property and equipment 88,129</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -56880,7 +56936,11 @@
           <t>Depreciation of property and equipment (Note 23)</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -59482,7 +59542,11 @@
           <t>Depreciation of property and equipment (Note 24)</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -61758,7 +61822,11 @@
           <t>Depreciation of property and equipment (Note 22)</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -65532,7 +65600,11 @@
           <t>Depreciation of property and equipment (Note 21)</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ACQ.xlsx
+++ b/output/pdf_financials_xlsx/ACQ.xlsx
@@ -2892,10 +2892,8 @@
       <c r="L37" s="3" t="n">
         <v>131.152</v>
       </c>
-      <c r="M37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M37" s="3" t="n">
+        <v>129.733</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>118.65</v>
@@ -3064,51 +3062,49 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.513</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>2.393</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>2.582</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>6.886</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.022</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>4.761</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>11.235</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>30.632</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>13.122</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>14.064</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>8.324</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>5.405</v>
       </c>
     </row>
     <row r="41">
@@ -3129,28 +3125,28 @@
         <v>35.323</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>42.448</v>
+        <v>43.961</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>47.944</v>
+        <v>50.337</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>57.771</v>
+        <v>60.353</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>92.13800000000001</v>
+        <v>97.908</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>90.821</v>
+        <v>100.361</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>85.587</v>
+        <v>92.473</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>79.931</v>
+        <v>84.556</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>131.152</v>
+        <v>136.174</v>
       </c>
       <c r="M41" s="1" t="inlineStr">
         <is>
@@ -3158,22 +3154,22 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>118.65</v>
+        <v>129.885</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>132.913</v>
+        <v>163.545</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>217.79</v>
+        <v>230.912</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>222.076</v>
+        <v>236.14</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>173.568</v>
+        <v>181.892</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>133.164</v>
+        <v>138.569</v>
       </c>
     </row>
     <row r="42">
@@ -4731,10 +4727,8 @@
       <c r="L64" s="3" t="n">
         <v>101.28</v>
       </c>
-      <c r="M64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M64" s="3" t="n">
+        <v>84.774</v>
       </c>
       <c r="N64" s="3" t="n">
         <v>137.51</v>
@@ -5095,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.000289</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -5127,22 +5121,22 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>24.079</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>25.602</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>27.766</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>28.411</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>35.78</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>25.872</v>
       </c>
     </row>
     <row r="71">
@@ -5160,7 +5154,7 @@
         <v>0.00057</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>9.6e-05</v>
+        <v>0.000385</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
@@ -5192,22 +5186,22 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>24.079</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>25.602</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>27.766</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>28.411</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>35.78</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>25.872</v>
       </c>
     </row>
     <row r="72">
@@ -5420,7 +5414,7 @@
         <v>0.139109</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>127.446348</v>
+        <v>127.446059</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>156.925</v>
@@ -5452,22 +5446,22 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>805.376</v>
+        <v>781.297</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>763.706</v>
+        <v>738.104</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>1067.583</v>
+        <v>1039.817</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1240.637</v>
+        <v>1212.226</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1113.808</v>
+        <v>1078.028</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>1040.585</v>
+        <v>1014.713</v>
       </c>
     </row>
     <row r="76">
@@ -5745,7 +5739,7 @@
         <v>0.3732066997554103</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0003261027577852206</v>
+        <v>0.0003302216204660443</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -5792,35 +5786,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>0.06274396376958875</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.04694109169849305</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.05384190267503079</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.05030017934631544</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.07223496349893405</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0.05367902136205952</v>
       </c>
     </row>
     <row r="81">
@@ -11704,7 +11686,11 @@
           <t>Lease liabilities (Note 24)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -14848,7 +14834,11 @@
           <t>Lease liabilities (Note 23)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -17356,7 +17346,11 @@
           <t>Lease liabilities (Note 25)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -20250,7 +20244,11 @@
           <t>Lease liabilities (Note 27) 21,208</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -35490,7 +35488,11 @@
           <t>Current portion of lease obligations (note 11) 907</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -35812,7 +35814,11 @@
           <t>Lease obligations (note 11) 120</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -71384,7 +71390,11 @@
           <t>Future income taxes (note 18)</t>
         </is>
       </c>
-      <c r="D591" t="inlineStr"/>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E591" t="inlineStr">
         <is>
           <t>-</t>
